--- a/fix-errors/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-technique-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-technique-imagerie|0.1.0</t>
   </si>
   <si>
     <t>FRLMProcedure</t>
@@ -184,7 +184,7 @@
     <t>FRCDADICOMTechniqueImagerie.participant</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-procedure-imaging-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-imaging-document|0.1.0</t>
   </si>
   <si>
     <t>FRProcedureImagingDocument</t>
